--- a/NECP Scenario/Results/Regional Results/EL63_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL63_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547326791217928E-12</v>
+        <v>2.284567424484828E-12</v>
       </c>
       <c r="C2">
-        <v>8.102406559653374E-13</v>
+        <v>1.196286979635818E-12</v>
       </c>
       <c r="D2">
-        <v>1.19047736122651E-12</v>
+        <v>1.757694583198882E-12</v>
       </c>
       <c r="E2">
-        <v>1.7492385396465E-12</v>
+        <v>2.582684323133426E-12</v>
       </c>
       <c r="F2">
-        <v>2.570230619458541E-12</v>
+        <v>3.79484673841272E-12</v>
       </c>
       <c r="G2">
-        <v>3.776468684161245E-12</v>
+        <v>5.575810550831557E-12</v>
       </c>
       <c r="H2">
-        <v>2.288777660453223E-11</v>
+        <v>3.379308603470312E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.43333047726058E-08</v>
+        <v>7.997400869486613E-08</v>
       </c>
       <c r="C3">
-        <v>4.765357817198612E-08</v>
+        <v>7.000623245612369E-08</v>
       </c>
       <c r="D3">
-        <v>1.393497561518988E-07</v>
+        <v>2.04330642881288E-07</v>
       </c>
       <c r="E3">
-        <v>2.994767912867743E-07</v>
+        <v>3.911141626066323E-07</v>
       </c>
       <c r="F3">
-        <v>9.725064618289594E-07</v>
+        <v>1.126502019645231E-06</v>
       </c>
       <c r="G3">
-        <v>7.35414226133116E-06</v>
+        <v>2.567877681919679E-05</v>
       </c>
       <c r="H3">
-        <v>0.6018123477118688</v>
+        <v>0.8562557144213968</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.618330905919256E-08</v>
+        <v>6.797790739273433E-08</v>
       </c>
       <c r="C4">
-        <v>4.050554145219908E-08</v>
+        <v>5.950529759168309E-08</v>
       </c>
       <c r="D4">
-        <v>1.184472927351583E-07</v>
+        <v>1.736810464530962E-07</v>
       </c>
       <c r="E4">
-        <v>2.545552725998676E-07</v>
+        <v>3.324470382196886E-07</v>
       </c>
       <c r="F4">
-        <v>8.266304925606941E-07</v>
+        <v>9.575267167024746E-07</v>
       </c>
       <c r="G4">
-        <v>6.251020922137567E-06</v>
+        <v>2.182696029632131E-05</v>
       </c>
       <c r="H4">
-        <v>0.511540495555046</v>
+        <v>0.7278173572582222</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.4098300293615716</v>
+        <v>0.4081039127024115</v>
       </c>
       <c r="D5">
-        <v>0.4058177617799874</v>
+        <v>0.4036977838096689</v>
       </c>
       <c r="E5">
-        <v>0.400234807185634</v>
+        <v>0.3998440021649719</v>
       </c>
       <c r="F5">
-        <v>0.3902916448077364</v>
+        <v>0.3899389458146388</v>
       </c>
       <c r="G5">
-        <v>0.3801783903067376</v>
+        <v>0.3797959573629528</v>
       </c>
       <c r="H5">
-        <v>0.3702313870201603</v>
+        <v>0.3697370767096131</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.1424286878209463</v>
+        <v>0.1425515595435012</v>
       </c>
       <c r="C7">
-        <v>1.311546247577274</v>
+        <v>1.306477222147769</v>
       </c>
       <c r="D7">
-        <v>1.28395922011763</v>
+        <v>1.277559565041079</v>
       </c>
       <c r="E7">
-        <v>1.2629861117856</v>
+        <v>1.262986111666522</v>
       </c>
       <c r="F7">
-        <v>1.22600000071317</v>
+        <v>1.226000000581563</v>
       </c>
       <c r="G7">
-        <v>1.188333333922929</v>
+        <v>1.1883333336839</v>
       </c>
       <c r="H7">
-        <v>1.150666665887972</v>
+        <v>1.150666665006888</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.04980024049310625</v>
+        <v>0.04984320263208386</v>
       </c>
       <c r="C9">
-        <v>0.04875257468452497</v>
+        <v>0.04870630482888631</v>
       </c>
       <c r="D9">
-        <v>0.04311902846810427</v>
+        <v>0.04300136480184912</v>
       </c>
       <c r="E9">
-        <v>0.0413687283995639</v>
+        <v>0.04175953337654591</v>
       </c>
       <c r="F9">
-        <v>0.03837968410676588</v>
+        <v>0.0387323830508909</v>
       </c>
       <c r="G9">
-        <v>0.03532277539147591</v>
+        <v>0.03570520824736527</v>
       </c>
       <c r="H9">
-        <v>0.03209961498349902</v>
+        <v>0.03259392495971794</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1.179275115194248E-07</v>
+        <v>1.70265328890892E-07</v>
       </c>
       <c r="D10">
-        <v>1.235915205462643E-07</v>
+        <v>1.877305657822344E-07</v>
       </c>
       <c r="E10">
-        <v>1.175230458732497E-07</v>
+        <v>1.74254511630759E-07</v>
       </c>
       <c r="F10">
-        <v>9.119925161914325E-08</v>
+        <v>1.331085109846108E-07</v>
       </c>
       <c r="G10">
-        <v>8.472856051274735E-08</v>
+        <v>1.262770957159645E-07</v>
       </c>
       <c r="H10">
-        <v>4.206111165130465E-07</v>
+        <v>6.342548663976852E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.592419914823684</v>
+        <v>2.592419917261071</v>
       </c>
       <c r="C14">
-        <v>2.6335762061398</v>
+        <v>2.633576204427221</v>
       </c>
       <c r="D14">
-        <v>2.895512797749595</v>
+        <v>2.895512788090519</v>
       </c>
       <c r="E14">
-        <v>3.45748582419431</v>
+        <v>3.457485778347098</v>
       </c>
       <c r="F14">
-        <v>4.18614549375233</v>
+        <v>4.18614433243886</v>
       </c>
       <c r="G14">
-        <v>4.12570361333049</v>
+        <v>4.125703653130952</v>
       </c>
       <c r="H14">
-        <v>5.372817139128961</v>
+        <v>5.372817365700789</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.603343744548145E-08</v>
+        <v>6.775050946151228E-08</v>
       </c>
       <c r="C19">
-        <v>4.403943644681293E-08</v>
+        <v>6.471436010495513E-08</v>
       </c>
       <c r="D19">
-        <v>1.060048796684592E-07</v>
+        <v>1.571307207407838E-07</v>
       </c>
       <c r="E19">
-        <v>2.348813514465933E-07</v>
+        <v>3.254087611618302E-07</v>
       </c>
       <c r="F19">
-        <v>6.695340429037874E-07</v>
+        <v>8.586771926713917E-07</v>
       </c>
       <c r="G19">
-        <v>1.281666011112318E-06</v>
+        <v>2.184244648692405E-06</v>
       </c>
       <c r="H19">
-        <v>7.199402364522949E-06</v>
+        <v>1.352655835316204E-05</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.68267499602527E-08</v>
+        <v>5.420040757256788E-08</v>
       </c>
       <c r="C21">
-        <v>3.523154915745033E-08</v>
+        <v>5.177148808396408E-08</v>
       </c>
       <c r="D21">
-        <v>8.480390373476744E-08</v>
+        <v>1.25704576592627E-07</v>
       </c>
       <c r="E21">
-        <v>1.879050811572746E-07</v>
+        <v>2.603270089294641E-07</v>
       </c>
       <c r="F21">
-        <v>5.356272343230296E-07</v>
+        <v>6.869417541371135E-07</v>
       </c>
       <c r="G21">
-        <v>1.025332808889856E-06</v>
+        <v>1.747395718953923E-06</v>
       </c>
       <c r="H21">
-        <v>5.759521891618362E-06</v>
+        <v>1.082124668252964E-05</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1.415685490587809E-08</v>
+        <v>2.115538925378061E-08</v>
       </c>
       <c r="D22">
-        <v>2.054011721354226E-08</v>
+        <v>3.148572358767771E-08</v>
       </c>
       <c r="E22">
-        <v>4.895883057887072E-08</v>
+        <v>7.294864538490686E-08</v>
       </c>
       <c r="F22">
-        <v>1.931240682630563E-07</v>
+        <v>2.558936687242289E-07</v>
       </c>
       <c r="G22">
-        <v>1.432441828590714E-06</v>
+        <v>2.753459388548232E-06</v>
       </c>
       <c r="H22">
-        <v>0.7525637172753603</v>
+        <v>0.7525637173857059</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1083,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1.234314365324719</v>
+        <v>1.234314365200555</v>
       </c>
       <c r="C23">
-        <v>1.234314365433005</v>
+        <v>1.234314365359168</v>
       </c>
       <c r="D23">
-        <v>1.23431436536008</v>
+        <v>1.23431436525417</v>
       </c>
       <c r="E23">
-        <v>1.234314365298103</v>
+        <v>1.234314365158373</v>
       </c>
       <c r="F23">
-        <v>1.234314365201985</v>
+        <v>1.234314365017137</v>
       </c>
       <c r="G23">
-        <v>1.234314365021601</v>
+        <v>1.234314364753992</v>
       </c>
       <c r="H23">
-        <v>1.234314361818449</v>
+        <v>1.234314360100415</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.276142756655451E-08</v>
+        <v>1.887841668991685E-08</v>
       </c>
       <c r="C24">
-        <v>2.05326560404958E-07</v>
+        <v>2.966527101652303E-07</v>
       </c>
       <c r="D24">
-        <v>2.143058177058892E-07</v>
+        <v>3.251860121813309E-07</v>
       </c>
       <c r="E24">
-        <v>2.053190266607687E-07</v>
+        <v>3.043314899025485E-07</v>
       </c>
       <c r="F24">
-        <v>1.620625427787096E-07</v>
+        <v>2.366513041923742E-07</v>
       </c>
       <c r="G24">
-        <v>1.537079885721516E-07</v>
+        <v>2.288759972603742E-07</v>
       </c>
       <c r="H24">
-        <v>7.680971878770724E-07</v>
+        <v>1.155554136689635E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>4.577910563920804E-09</v>
+        <v>6.772249126230805E-09</v>
       </c>
       <c r="C25">
-        <v>2.586475762392611E-09</v>
+        <v>3.805865210757212E-09</v>
       </c>
       <c r="D25">
-        <v>2.835071911046379E-09</v>
+        <v>4.185865860383394E-09</v>
       </c>
       <c r="E25">
-        <v>3.666097232687954E-09</v>
+        <v>5.399718348858322E-09</v>
       </c>
       <c r="F25">
-        <v>4.146152939576515E-09</v>
+        <v>6.092530426388942E-09</v>
       </c>
       <c r="G25">
-        <v>4.971678265265345E-09</v>
+        <v>7.335868321575005E-09</v>
       </c>
       <c r="H25">
-        <v>2.797870563969465E-08</v>
+        <v>4.122909472113824E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1.380204704211837E-08</v>
+        <v>2.031797995619179E-08</v>
       </c>
       <c r="D27">
-        <v>5.364458632890562E-08</v>
+        <v>7.807000060601561E-08</v>
       </c>
       <c r="E27">
-        <v>1.757364046075622E-07</v>
+        <v>2.799270031182144E-07</v>
       </c>
       <c r="F27">
-        <v>6.913921762106294E-07</v>
+        <v>1.832821484622003E-06</v>
       </c>
       <c r="G27">
-        <v>0.07194245657997995</v>
+        <v>0.1023134953009959</v>
       </c>
       <c r="H27">
-        <v>0.7916626955339557</v>
+        <v>1.188589328808498</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.4258579342040935</v>
+        <v>0.3933648413488999</v>
       </c>
       <c r="D30">
-        <v>0.6469791336736516</v>
+        <v>0.7781065769921963</v>
       </c>
       <c r="E30">
-        <v>1.563879501812717</v>
+        <v>1.399070806810481</v>
       </c>
       <c r="F30">
-        <v>1.797742819188603</v>
+        <v>1.573709776877524</v>
       </c>
       <c r="G30">
-        <v>2.169475126870426</v>
+        <v>1.878342394136967</v>
       </c>
       <c r="H30">
-        <v>3.616880448679713</v>
+        <v>3.604398959875857</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.6042064001719376</v>
+        <v>0.604206397435855</v>
       </c>
       <c r="C31">
-        <v>0.6042062705348441</v>
+        <v>0.6042062067934514</v>
       </c>
       <c r="D31">
-        <v>0.6041997835625479</v>
+        <v>0.6041960855730154</v>
       </c>
       <c r="E31">
-        <v>0.6020221231254314</v>
+        <v>0.6016414442945888</v>
       </c>
       <c r="F31">
-        <v>0.5973911475255687</v>
+        <v>0.5956651007417861</v>
       </c>
       <c r="G31">
-        <v>0.5882080106228875</v>
+        <v>0.5889273816642934</v>
       </c>
       <c r="H31">
-        <v>0.5942016823061831</v>
+        <v>0.5868344924330003</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>8.017346574927445E-09</v>
+        <v>1.192763809571572E-08</v>
       </c>
       <c r="D32">
-        <v>2.556851840751622E-08</v>
+        <v>4.012790433297642E-08</v>
       </c>
       <c r="E32">
-        <v>7.480159193536043E-08</v>
+        <v>1.282992703229341E-07</v>
       </c>
       <c r="F32">
-        <v>4.150665332769247E-07</v>
+        <v>1.589266734650942E-06</v>
       </c>
       <c r="G32">
-        <v>0.8367752306139312</v>
+        <v>0.8367752124507445</v>
       </c>
       <c r="H32">
-        <v>0.8373845398746598</v>
+        <v>0.8373844246182234</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.02388966662793384</v>
+        <v>0.02388966420081879</v>
       </c>
       <c r="C33">
-        <v>0.02388966744847629</v>
+        <v>0.0238896652529392</v>
       </c>
       <c r="D33">
-        <v>0.02388966134800917</v>
+        <v>0.02388965646181864</v>
       </c>
       <c r="E33">
-        <v>0.02388965614333897</v>
+        <v>0.02388964851899608</v>
       </c>
       <c r="F33">
-        <v>0.02388964593658949</v>
+        <v>0.02388963306825979</v>
       </c>
       <c r="G33">
-        <v>0.02384154849471018</v>
+        <v>0.02384152689624405</v>
       </c>
       <c r="H33">
-        <v>0.02388943212391826</v>
+        <v>0.02388932103912896</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>7.564571694289912E-09</v>
+        <v>1.121512597324147E-08</v>
       </c>
       <c r="D34">
-        <v>9.810542552733193E-09</v>
+        <v>1.471426515577503E-08</v>
       </c>
       <c r="E34">
-        <v>1.644792237606055E-08</v>
+        <v>2.475795313642561E-08</v>
       </c>
       <c r="F34">
-        <v>2.573141290173544E-08</v>
+        <v>3.868924456257348E-08</v>
       </c>
       <c r="G34">
-        <v>3.679637936783621E-08</v>
+        <v>5.444707954301818E-08</v>
       </c>
       <c r="H34">
-        <v>2.142995538567551E-07</v>
+        <v>3.29997817664522E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.1034740391890682</v>
+        <v>0.1034740391822035</v>
       </c>
       <c r="C35">
-        <v>0.1034740366903378</v>
+        <v>0.1034740354870045</v>
       </c>
       <c r="D35">
-        <v>0.1034740352624351</v>
+        <v>0.1034740333616261</v>
       </c>
       <c r="E35">
-        <v>0.1034740328042749</v>
+        <v>0.1034740274355846</v>
       </c>
       <c r="F35">
-        <v>0.103473675913827</v>
+        <v>0.1034735055488328</v>
       </c>
       <c r="G35">
-        <v>0.1034734428987964</v>
+        <v>0.1034731386117737</v>
       </c>
       <c r="H35">
-        <v>0.1034711890969939</v>
+        <v>0.1034686591391018</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.4603336751518223</v>
+        <v>0.2230540616929026</v>
       </c>
       <c r="D36">
-        <v>0.4350871621824494</v>
+        <v>0.2091673436347211</v>
       </c>
       <c r="E36">
-        <v>0.4150783327130759</v>
+        <v>0.2015562957656832</v>
       </c>
       <c r="F36">
-        <v>0.4132817319454178</v>
+        <v>0.2004975589173132</v>
       </c>
       <c r="G36">
-        <v>0.415411798806631</v>
+        <v>0.2050321018538752</v>
       </c>
       <c r="H36">
-        <v>0.4417280718574156</v>
+        <v>0.2129191319707841</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>1.053767289022239</v>
+        <v>1.053767283918206</v>
       </c>
       <c r="C37">
-        <v>1.033506693789515</v>
+        <v>1.032143809383121</v>
       </c>
       <c r="D37">
-        <v>0.9733419115136183</v>
+        <v>0.9633548530547867</v>
       </c>
       <c r="E37">
-        <v>0.9178462968337443</v>
+        <v>0.9068318136394826</v>
       </c>
       <c r="F37">
-        <v>0.9146424284575766</v>
+        <v>0.9028280257090474</v>
       </c>
       <c r="G37">
-        <v>0.9204467062669076</v>
+        <v>0.9238375103144569</v>
       </c>
       <c r="H37">
-        <v>0.9768668677320502</v>
+        <v>0.9610600568132776</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.002111737128764487</v>
+        <v>0.002111747402859817</v>
       </c>
       <c r="C38">
-        <v>0.03765906202454383</v>
+        <v>0.03367924178118841</v>
       </c>
       <c r="D38">
-        <v>0.1230893055464956</v>
+        <v>0.116378276055435</v>
       </c>
       <c r="E38">
-        <v>0.2038954486310433</v>
+        <v>0.186672641580148</v>
       </c>
       <c r="F38">
-        <v>0.2200358306008701</v>
+        <v>0.2054604233823193</v>
       </c>
       <c r="G38">
-        <v>0.2658670918073258</v>
+        <v>0.2397022088684571</v>
       </c>
       <c r="H38">
-        <v>0.4154440490063394</v>
+        <v>0.6035066593671514</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>1.003667422180872E-07</v>
+        <v>1.477245181563784E-07</v>
       </c>
       <c r="C40">
-        <v>9.169301461879904E-08</v>
+        <v>1.347205925610788E-07</v>
       </c>
       <c r="D40">
-        <v>2.453546358203581E-07</v>
+        <v>3.614613636220719E-07</v>
       </c>
       <c r="E40">
-        <v>5.343581427333675E-07</v>
+        <v>7.165229237684625E-07</v>
       </c>
       <c r="F40">
-        <v>1.642040504732747E-06</v>
+        <v>1.985179212316623E-06</v>
       </c>
       <c r="G40">
-        <v>8.635808272443478E-06</v>
+        <v>2.78630214678892E-05</v>
       </c>
       <c r="H40">
-        <v>0.6018195471142332</v>
+        <v>0.85626924097975</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>8.301005901944526E-08</v>
+        <v>1.221783149653022E-07</v>
       </c>
       <c r="C41">
-        <v>7.573709060964942E-08</v>
+        <v>1.112767856756472E-07</v>
       </c>
       <c r="D41">
-        <v>2.032511964699257E-07</v>
+        <v>2.993856230457231E-07</v>
       </c>
       <c r="E41">
-        <v>4.424603537571422E-07</v>
+        <v>5.927740471491527E-07</v>
       </c>
       <c r="F41">
-        <v>1.362257726883724E-06</v>
+        <v>1.644468470839588E-06</v>
       </c>
       <c r="G41">
-        <v>7.276353731027423E-06</v>
+        <v>2.357435601527524E-05</v>
       </c>
       <c r="H41">
-        <v>0.5115462550769376</v>
+        <v>0.7278281785049047</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-1.735668319864199E-08</v>
+        <v>-2.554620319107618E-08</v>
       </c>
       <c r="C42">
-        <v>-1.595592400914963E-08</v>
+        <v>-2.344380688543164E-08</v>
       </c>
       <c r="D42">
-        <v>-4.210343935043232E-08</v>
+        <v>-6.207574057634874E-08</v>
       </c>
       <c r="E42">
-        <v>-9.189778897622526E-08</v>
+        <v>-1.237488766193098E-07</v>
       </c>
       <c r="F42">
-        <v>-2.79782777849023E-07</v>
+        <v>-3.407107414770346E-07</v>
       </c>
       <c r="G42">
-        <v>-1.359454541416055E-06</v>
+        <v>-4.288665452613962E-06</v>
       </c>
       <c r="H42">
-        <v>-0.09027329203729562</v>
+        <v>-0.1284410624748453</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>-0.4002358777685317</v>
+        <v>-0.4002788233515987</v>
       </c>
       <c r="C43">
-        <v>-1.632953060927774</v>
+        <v>-1.360045083271163</v>
       </c>
       <c r="D43">
-        <v>-1.491728454597242</v>
+        <v>-1.384707774741095</v>
       </c>
       <c r="E43">
-        <v>-1.750171699256198</v>
+        <v>-1.360446009521415</v>
       </c>
       <c r="F43">
-        <v>-1.217941188526677</v>
+        <v>-0.7675857380420883</v>
       </c>
       <c r="G43">
-        <v>-1.708871625969651</v>
+        <v>-1.241838518097795</v>
       </c>
       <c r="H43">
-        <v>-3.341280938151668</v>
+        <v>-3.435572950752075</v>
       </c>
     </row>
     <row r="44" spans="1:8">
